--- a/artfynd/A 31411-2025 artfynd.xlsx
+++ b/artfynd/A 31411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131007389</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131007388</v>
       </c>
       <c r="B3" t="n">
-        <v>99014</v>
+        <v>99015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131007391</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131007386</v>
       </c>
       <c r="B5" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31411-2025 artfynd.xlsx
+++ b/artfynd/A 31411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131007389</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131007388</v>
       </c>
       <c r="B3" t="n">
-        <v>99015</v>
+        <v>99018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31411-2025 artfynd.xlsx
+++ b/artfynd/A 31411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131007389</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131007388</v>
       </c>
       <c r="B3" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131007391</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131007386</v>
       </c>
       <c r="B5" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31411-2025 artfynd.xlsx
+++ b/artfynd/A 31411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131007389</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131007388</v>
       </c>
       <c r="B3" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>131007391</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131007386</v>
       </c>
       <c r="B5" t="n">
-        <v>79270</v>
+        <v>79272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31411-2025 artfynd.xlsx
+++ b/artfynd/A 31411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131007389</v>
+        <v>131007391</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520153</v>
+        <v>520137</v>
       </c>
       <c r="R2" t="n">
-        <v>6671130</v>
+        <v>6671131</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -768,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131007388</v>
+        <v>131007386</v>
       </c>
       <c r="B3" t="n">
-        <v>99021</v>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kärrgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520172</v>
+        <v>520260</v>
       </c>
       <c r="R3" t="n">
-        <v>6671030</v>
+        <v>6670928</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skott</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131007391</v>
+        <v>131007388</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärrgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520137</v>
+        <v>520172</v>
       </c>
       <c r="R4" t="n">
-        <v>6671131</v>
+        <v>6671030</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,6 +946,11 @@
           <t>2025-11-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skott</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -968,103 +972,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131007386</v>
-      </c>
-      <c r="B5" t="n">
-        <v>79272</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6434</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Nästlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bryoria furcellata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kärrgruvan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>520260</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6670928</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Norrbärke</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Sara Lundkvist</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Sara Lundkvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
